--- a/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -1388,7 +1388,7 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7094.386718944054</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="C2" t="n">
         <v>0.9957648995493169</v>
@@ -1397,13 +1397,13 @@
         <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.678870188120528</v>
+        <v>1.678870188120527</v>
       </c>
       <c r="F2" t="n">
         <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67804342107184</v>
+        <v>1.678043421071839</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.667251009830694</v>
+        <v>1.667251009830693</v>
       </c>
       <c r="C2" t="n">
-        <v>0.103950564589624</v>
+        <v>0.1039505645896223</v>
       </c>
       <c r="D2" t="n">
-        <v>1.463511647062426</v>
+        <v>1.463511647062429</v>
       </c>
       <c r="E2" t="n">
-        <v>1.870990372598961</v>
+        <v>1.870990372598958</v>
       </c>
       <c r="F2" t="n">
-        <v>6.837236032515922e-58</v>
+        <v>6.837236032486468e-58</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02463484865352594</v>
+        <v>-0.02463484865352595</v>
       </c>
       <c r="C3" t="n">
         <v>0.02140527657651924</v>
@@ -1498,10 +1498,10 @@
         <v>-0.06658841982262248</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01731872251557061</v>
+        <v>0.01731872251557058</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2497826842838106</v>
+        <v>0.2497826842838102</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.07540915009642361</v>
+        <v>-0.0754091500964236</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05279509857940832</v>
+        <v>0.05279509857940829</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1788856418723057</v>
+        <v>-0.1788856418723056</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02806734167945846</v>
+        <v>0.02806734167945842</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1531951152281507</v>
+        <v>0.1531951152281506</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.07777010843832736</v>
+        <v>-0.07777010843832738</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03746669966516231</v>
+        <v>0.0374666996651623</v>
       </c>
       <c r="D5" t="n">
         <v>-0.1512034904016244</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004336726475030334</v>
+        <v>-0.004336726475030375</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03792052047519413</v>
+        <v>0.03792052047519403</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02910393820822493</v>
+        <v>0.02910393820822508</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03598696595065996</v>
+        <v>0.03598696595065994</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0414292189679378</v>
+        <v>-0.04142921896793762</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09963709538438767</v>
+        <v>0.09963709538438777</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4186672829157784</v>
+        <v>0.4186672829157758</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0238152894120912</v>
+        <v>0.02381528941209119</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03444948165300097</v>
+        <v>0.03444948165300096</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04370445391386407</v>
+        <v>-0.04370445391386405</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09133503273804647</v>
+        <v>0.09133503273804644</v>
       </c>
       <c r="F7" t="n">
         <v>0.489370415995682</v>
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03400947065252904</v>
+        <v>0.03400947065252902</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03572753009575889</v>
+        <v>0.03572753009575888</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03601520159172927</v>
+        <v>-0.03601520159172925</v>
       </c>
       <c r="E8" t="n">
         <v>0.1040341428967873</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03806830840584246</v>
+        <v>0.03806830840584247</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03435019598273854</v>
+        <v>0.03435019598273852</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.02925683858221754</v>
+        <v>-0.02925683858221748</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1053934553939025</v>
+        <v>0.1053934553939024</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2677575867271222</v>
+        <v>0.2677575867271219</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002048208353331531</v>
+        <v>0.002048208353331629</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05422289275560442</v>
+        <v>0.05422289275560438</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1042267085852309</v>
+        <v>-0.1042267085852308</v>
       </c>
       <c r="E10" t="n">
         <v>0.108323125291894</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9698679804037615</v>
+        <v>0.9698679804037601</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.002592226077109175</v>
+        <v>-0.002592226077109182</v>
       </c>
       <c r="C11" t="n">
         <v>0.05602652915899779</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.09685847877529365</v>
+        <v>-0.09685847877529374</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05376448018771039</v>
+        <v>0.05376448018771034</v>
       </c>
       <c r="D12" t="n">
         <v>-0.2022349235907233</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008517966040135994</v>
+        <v>0.008517966040135813</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07161892986848868</v>
+        <v>0.07161892986848817</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05872986129122747</v>
+        <v>0.05872986129122744</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05289827688087845</v>
+        <v>0.05289827688087843</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.04494885623952209</v>
+        <v>-0.04494885623952206</v>
       </c>
       <c r="E13" t="n">
         <v>0.162408578821977</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01177434185712835</v>
+        <v>0.01177434185712845</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05286151476865353</v>
+        <v>0.05286151476865345</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09183232325766474</v>
+        <v>-0.09183232325766447</v>
       </c>
       <c r="E14" t="n">
         <v>0.1153810069719214</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8237383381340895</v>
+        <v>0.8237383381340877</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,16 +1789,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08022934381684162</v>
+        <v>-0.08022934381684163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05335891402080915</v>
+        <v>0.05335891402080917</v>
       </c>
       <c r="D15" t="n">
         <v>-0.1848108935517969</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02435220591811364</v>
+        <v>0.02435220591811366</v>
       </c>
       <c r="F15" t="n">
         <v>0.1326897956946211</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02854452070261685</v>
+        <v>0.02854452070261681</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0524417782095568</v>
+        <v>0.05244177820955667</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07423947587335188</v>
+        <v>-0.07423947587335167</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1313285172785856</v>
+        <v>0.1313285172785853</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5862290010152384</v>
+        <v>0.586229001015238</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,16 +1839,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.009535077288637601</v>
+        <v>0.00953507728863757</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05256744027004785</v>
+        <v>0.05256744027004769</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09349521240011668</v>
+        <v>-0.09349521240011638</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1125653669773919</v>
+        <v>0.1125653669773915</v>
       </c>
       <c r="F17" t="n">
         <v>0.8560634189937375</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09439860867570241</v>
+        <v>-0.09439860867570243</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05484958712397588</v>
+        <v>0.05484958712397583</v>
       </c>
       <c r="D18" t="n">
         <v>-0.201901824005587</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0131046066541822</v>
+        <v>0.01310460665418209</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08524265511921764</v>
+        <v>0.08524265511921732</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03376783026243109</v>
+        <v>-0.03376783026243111</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05194237008077477</v>
+        <v>0.05194237008077476</v>
       </c>
       <c r="D19" t="n">
         <v>-0.1355730048924005</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06803734436753832</v>
+        <v>0.06803734436753828</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5156264420353127</v>
+        <v>0.5156264420353125</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.02764259828225421</v>
+        <v>-0.02764259828225423</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05243646023149125</v>
+        <v>0.05243646023149124</v>
       </c>
       <c r="D20" t="n">
         <v>-0.1304161718127439</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07513097524823546</v>
+        <v>0.07513097524823542</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5980799157062464</v>
+        <v>0.598079915706246</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05277599238898848</v>
+        <v>-0.05277599238898849</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05170157742489209</v>
+        <v>0.05170157742489204</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1541092220856861</v>
+        <v>-0.154109222085686</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04855723730770913</v>
+        <v>0.04855723730770903</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3073581670729142</v>
+        <v>0.3073581670729137</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03816573212201307</v>
+        <v>-0.03816573212201323</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05200730262192996</v>
+        <v>0.05200730262192984</v>
       </c>
       <c r="D22" t="n">
         <v>-0.1400981721940713</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06376670795004519</v>
+        <v>0.06376670795004477</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4630381345915038</v>
+        <v>0.4630381345915006</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.05938706149335551</v>
+        <v>-0.05938706149335556</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05429573538926734</v>
+        <v>0.05429573538926729</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1658047473704364</v>
+        <v>-0.1658047473704363</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04703062438372533</v>
+        <v>0.04703062438372518</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2740557435063636</v>
+        <v>0.274055743506363</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.008451758672660589</v>
+        <v>0.008451758672660556</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04715478622950783</v>
+        <v>0.04715478622950785</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08396992403586005</v>
+        <v>-0.08396992403586014</v>
       </c>
       <c r="E24" t="n">
         <v>0.1008734413811812</v>
       </c>
       <c r="F24" t="n">
-        <v>0.857753672816564</v>
+        <v>0.8577536728165647</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.008266388421399361</v>
+        <v>0.008266388421399316</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02616363601935622</v>
+        <v>0.0261636360193562</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04301339588115373</v>
+        <v>-0.04301339588115374</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05954617272395245</v>
+        <v>0.05954617272395238</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7520408188561629</v>
+        <v>0.752040818856164</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02423811373715813</v>
+        <v>0.02423811373715803</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03264857083897</v>
+        <v>0.03264857083897001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03975190925392773</v>
+        <v>-0.03975190925392785</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08822813672824399</v>
+        <v>0.08822813672824389</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4578484564206015</v>
+        <v>0.4578484564206033</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2092,16 +2092,16 @@
         <v>-0.0391593403491267</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03173000514229339</v>
+        <v>0.03173000514229343</v>
       </c>
       <c r="D27" t="n">
         <v>-0.1013490076572925</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02303032695903906</v>
+        <v>0.02303032695903913</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2171498974623944</v>
+        <v>0.2171498974623949</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0192295424242075</v>
+        <v>0.01922954242420746</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03227805668499568</v>
+        <v>0.0322780566849957</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04403428616932635</v>
+        <v>-0.04403428616932643</v>
       </c>
       <c r="E28" t="n">
         <v>0.08249337101774136</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5513445242495112</v>
+        <v>0.5513445242495123</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2142,16 +2142,16 @@
         <v>0.06730170037260196</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03196767543970733</v>
+        <v>0.03196767543970735</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004646207841309952</v>
+        <v>0.004646207841309924</v>
       </c>
       <c r="E29" t="n">
         <v>0.129957192903894</v>
       </c>
       <c r="F29" t="n">
-        <v>0.035264785038513</v>
+        <v>0.0352647850385131</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.04059280522771685</v>
+        <v>-0.0405928052277169</v>
       </c>
       <c r="C30" t="n">
         <v>0.04219295914182773</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1232894855468692</v>
+        <v>-0.1232894855468693</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04210387509143552</v>
+        <v>0.04210387509143548</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3360117637295977</v>
+        <v>0.3360117637295972</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0009948915328936545</v>
+        <v>-0.02814404589903955</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001577711740423721</v>
+        <v>0.02420739120983631</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004087149722110155</v>
+        <v>-0.07558966082999022</v>
       </c>
       <c r="E31" t="n">
-        <v>0.002097366656322845</v>
+        <v>0.01930156903191111</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5283076912307983</v>
+        <v>0.2449828954760783</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.003364288003062576</v>
+        <v>0.4490526515310966</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001764656162787906</v>
+        <v>0.01068393144388238</v>
       </c>
       <c r="D32" t="n">
-        <v>-9.437452109837185e-05</v>
+        <v>0.4281125306877921</v>
       </c>
       <c r="E32" t="n">
-        <v>0.006822950527223523</v>
+        <v>0.4699927723744011</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05658749372658557</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.375687514584261e-05</v>
+        <v>0.003364288003062581</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004788621486128006</v>
+        <v>0.001764656162787883</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.009351768773259718</v>
+        <v>-9.437452109831981e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>0.009419282523551403</v>
+        <v>0.006822950527223481</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9943754446863979</v>
+        <v>0.05658749372658183</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4490526515310966</v>
+        <v>-0.0009948915328936501</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01068393144388248</v>
+        <v>0.00157771174042372</v>
       </c>
       <c r="D34" t="n">
-        <v>0.428112530687792</v>
+        <v>-0.004087149722110148</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4699927723744013</v>
+        <v>0.002097366656322847</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.5283076912308</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.02814404589903955</v>
+        <v>3.375687514584298e-05</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02420739120983631</v>
+        <v>0.004788621486128021</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0755896608299902</v>
+        <v>-0.00935176877325975</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01930156903191111</v>
+        <v>0.009419282523551434</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2449828954760783</v>
+        <v>0.9943754446863978</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2314,19 +2314,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001861597274177133</v>
+        <v>0.001861597274177134</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001577846052651465</v>
+        <v>0.001577846052651468</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.001230924162168428</v>
+        <v>-0.001230924162168433</v>
       </c>
       <c r="E36" t="n">
-        <v>0.004954118710522693</v>
+        <v>0.0049541187105227</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2380660284989626</v>
+        <v>0.2380660284989632</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802938</v>
+        <v>-2.680600179802939</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981325</v>
+        <v>0.4771933030981503</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768271168e-08</v>
+        <v>1.938181768273511e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,7 +2394,7 @@
         <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033997</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
         <v>0.79975540801217</v>
@@ -2410,10 +2410,10 @@
         <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442914</v>
+        <v>0.2335027157442915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069159</v>
+        <v>0.3364439424069162</v>
       </c>
     </row>
     <row r="5">
@@ -2426,10 +2426,10 @@
         <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734026513921177</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054277e-06</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387295</v>
+        <v>0.03527526670387308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.191688294691954</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.853994545471355</v>
+        <v>0.8539945454713548</v>
       </c>
     </row>
     <row r="7">
@@ -2458,10 +2458,10 @@
         <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133382</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125516</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2474,10 +2474,10 @@
         <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982443</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432464</v>
+        <v>0.5954095400432469</v>
       </c>
     </row>
     <row r="9">
@@ -2490,10 +2490,10 @@
         <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409136</v>
+        <v>0.1695280942409139</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342701e-07</v>
+        <v>2.539495077342821e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04456520772617086</v>
+        <v>-0.0445652077261707</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604021031716313</v>
+        <v>0.260402103171632</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517834</v>
+        <v>0.8641137091517843</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798149</v>
+        <v>-0.2737623724798146</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465057</v>
+        <v>0.2787881385465067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3261132423877617</v>
+        <v>0.326113242387764</v>
       </c>
     </row>
     <row r="12">
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118127</v>
+        <v>0.08100487957118148</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097166</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
         <v>0.7550514391424692</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461736</v>
+        <v>0.03917827337461754</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743769</v>
+        <v>0.2572958805743774</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123745</v>
+        <v>0.8789745077123743</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307947</v>
+        <v>-0.05296103812307935</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588713</v>
+        <v>0.2610089865588724</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375523</v>
+        <v>0.8392062624375534</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534159</v>
+        <v>0.1181322726534161</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577177</v>
+        <v>0.2572294350577187</v>
       </c>
       <c r="D15" t="n">
-        <v>0.646055612898408</v>
+        <v>0.6460556128984086</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379581</v>
+        <v>-0.004000986240379481</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311186</v>
+        <v>0.2383903410311192</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655129</v>
+        <v>0.9866094604655132</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395304</v>
+        <v>0.1057185310395306</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421748</v>
+        <v>0.2543340222421759</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6776529122567303</v>
+        <v>0.677652912256731</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733256</v>
+        <v>-0.1377694895733254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313626</v>
+        <v>0.2636874203313636</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546261</v>
+        <v>0.6013412201546282</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223238</v>
+        <v>-0.02557154094223237</v>
       </c>
       <c r="C19" t="n">
-        <v>0.252759790153811</v>
+        <v>0.2527597901538116</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966675</v>
+        <v>0.9194160355966677</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376427</v>
+        <v>-0.07344622569376411</v>
       </c>
       <c r="C20" t="n">
-        <v>0.267457860954101</v>
+        <v>0.2674578609541021</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222772</v>
+        <v>0.7836169672222787</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305059</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244289653245072</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719846</v>
+        <v>0.3983578134719854</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362026</v>
+        <v>-0.1704634573362028</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696748454965904</v>
+        <v>0.269674845496591</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806361</v>
+        <v>0.5273167196806365</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334757</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.287067218044571</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08105838975171785</v>
+        <v>0.0810583897517186</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074267</v>
+        <v>0.9366864721074268</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923891e-10</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2746,10 +2746,10 @@
         <v>-0.5776106069409677</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421807</v>
+        <v>0.1143619392421806</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103943e-07</v>
+        <v>4.401383208103854e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.237316144844174</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377478</v>
+        <v>0.1503781926377481</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757813</v>
+        <v>0.1145360411757815</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998651</v>
+        <v>-0.04350476117998643</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386412</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400213</v>
+        <v>0.7872365295400221</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975732</v>
+        <v>-0.07514354096975739</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223567</v>
+        <v>0.1613683918223571</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120151</v>
+        <v>0.6414556246120158</v>
       </c>
     </row>
     <row r="29">
@@ -2807,29 +2807,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742097</v>
+        <v>0.09749293462742094</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290165</v>
+        <v>0.1543265796290169</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510008</v>
+        <v>0.5275624553510021</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002418133412192873</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007135781003458546</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7347043603418277</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
     <row r="31">
@@ -2839,45 +2839,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962195</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992455039</v>
+        <v>0.008304876992454899</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341576</v>
+        <v>0.5461741835341518</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004129656026475419</v>
+        <v>-0.002418133412192865</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02222260881033174</v>
+        <v>0.007135781003458533</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8525770672961279</v>
+        <v>0.7347043603418282</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2280638724458785</v>
+        <v>-0.004129656026475429</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.02222260881033176</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04668969945129923</v>
+        <v>0.8525770672961277</v>
       </c>
     </row>
     <row r="34">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474495</v>
+        <v>0.006335499136474494</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197181</v>
+        <v>0.006871422968197173</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666435</v>
+        <v>0.3565249957666431</v>
       </c>
     </row>
   </sheetData>
